--- a/reports/pdf_change_20260928.xlsx
+++ b/reports/pdf_change_20260928.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,927억   ·   현금 18억(0.4%)      당일 2026-09-28  vs  전영업일 2026-09-23      매수 8종목  /  매도 10종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,927억      당일 2026-09-28  vs  전영업일 2026-09-23      매수 8종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -883,23 +883,23 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>나노신소재</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>462896044</v>
+        <v>2359075214</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.64%→0.73%</t>
+          <t>0.47%→0.96%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>61→70</t>
+          <t>9→18</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -927,23 +927,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>나노신소재</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2359075214</v>
+        <v>462896044</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>0.47%→0.96%</t>
+          <t>0.64%→0.73%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>9→18</t>
+          <t>61→70</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -1071,7 +1071,7 @@
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,285억   ·   현금 59억(1.8%)      당일 2026-09-28  vs  전영업일 2026-09-23      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,285억      당일 2026-09-28  vs  전영업일 2026-09-23      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -1095,7 +1095,7 @@
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,689억   ·   현금 44억(1.6%)      당일 2026-09-28  vs  전영업일 2026-09-23      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,689억      당일 2026-09-28  vs  전영업일 2026-09-23      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
@@ -1119,7 +1119,7 @@
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,999억   ·   현금 35억(1.8%)      당일 2026-09-28  vs  전영업일 2026-09-23      매수 2종목  /  매도 4종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,999억      당일 2026-09-28  vs  전영업일 2026-09-23      매수 2종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
@@ -1354,7 +1354,7 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 299억   ·   현금 1억(0.4%)      당일 2026-09-28  vs  전영업일 2026-09-23      매수 3종목  /  매도 2종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 299억      당일 2026-09-28  vs  전영업일 2026-09-23      매수 3종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>

--- a/reports/pdf_change_20260928.xlsx
+++ b/reports/pdf_change_20260928.xlsx
@@ -883,23 +883,23 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>나노신소재</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2359075214</v>
+        <v>462896044</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.47%→0.96%</t>
+          <t>0.64%→0.73%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>9→18</t>
+          <t>61→70</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -927,23 +927,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>나노신소재</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>462896044</v>
+        <v>2359075214</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>0.64%→0.73%</t>
+          <t>0.47%→0.96%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>61→70</t>
+          <t>9→18</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">

--- a/reports/pdf_change_20260928.xlsx
+++ b/reports/pdf_change_20260928.xlsx
@@ -883,23 +883,23 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>나노신소재</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>462896044</v>
+        <v>2359075214</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.64%→0.73%</t>
+          <t>0.47%→0.96%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>61→70</t>
+          <t>9→18</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -927,23 +927,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>나노신소재</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2359075214</v>
+        <v>462896044</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>0.47%→0.96%</t>
+          <t>0.64%→0.73%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>9→18</t>
+          <t>61→70</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
